--- a/data/Saathi_Sneha_Care_Scheduling_Calendar_Mockup.xlsx
+++ b/data/Saathi_Sneha_Care_Scheduling_Calendar_Mockup.xlsx
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A2:K19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="15" min="1" max="1"/>
@@ -998,7 +998,6 @@
     <col width="28" customWidth="1" style="15" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="17.35" customHeight="1" s="16">
       <c r="B2" s="17" t="inlineStr">
         <is>
@@ -1013,7 +1012,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="21.75" customHeight="1" s="16">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -1657,7 +1655,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="16">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>BK-112</t>
         </is>
@@ -1665,44 +1663,154 @@
       <c r="B17" s="32" t="n">
         <v>46293</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>reena</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>General Checkup</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Dr. Ramesh Iyer</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Doctor</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>9741831772</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Approved by prashna</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>BK-113</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>2:00 PM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Prashna</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>mumbai general checkup</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Dr. Priya Nair</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Doctor</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>9741831772</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>adress:andheri</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>mumbai | Approved by Coordinator_Prashna</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BK-114</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3:00 PM - 4:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Prashna KC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dr. Priya Nair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Doctor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9741831772</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>gatkopar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Staged via Patient Chat | Approved by Coordinator_Prashna</t>
         </is>
       </c>
     </row>
